--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.49479396300911</v>
+        <v>4.46790401898898</v>
       </c>
       <c r="D2" t="n">
-        <v>43.29072725421725</v>
+        <v>7.034743178810304</v>
       </c>
       <c r="E2" t="n">
-        <v>25.31676038832282</v>
+        <v>4.113973563102458</v>
       </c>
       <c r="F2" t="n">
-        <v>23.84334595362643</v>
+        <v>3.874543717464294</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>95.17526354146773</v>
+        <v>15.46598032548851</v>
       </c>
       <c r="D3" t="n">
-        <v>95.25582615606511</v>
+        <v>15.47907175036058</v>
       </c>
       <c r="E3" t="n">
-        <v>25.31676038832282</v>
+        <v>4.113973563102458</v>
       </c>
       <c r="F3" t="n">
-        <v>23.84334595362643</v>
+        <v>3.874543717464294</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.688895381816906</v>
+        <v>1.411945499545247</v>
       </c>
       <c r="D4" t="n">
-        <v>36.77381434454428</v>
+        <v>5.975744830988447</v>
       </c>
       <c r="E4" t="n">
-        <v>25.31676038832282</v>
+        <v>4.113973563102458</v>
       </c>
       <c r="F4" t="n">
-        <v>23.84334595362643</v>
+        <v>3.874543717464294</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.5465437006232</v>
+        <v>4.47631335135127</v>
       </c>
       <c r="D5" t="n">
-        <v>14.17655220563588</v>
+        <v>2.303689733415831</v>
       </c>
       <c r="E5" t="n">
-        <v>25.31676038832282</v>
+        <v>4.113973563102458</v>
       </c>
       <c r="F5" t="n">
-        <v>23.84334595362643</v>
+        <v>3.874543717464294</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.22501912754344</v>
+        <v>4.91156560822581</v>
       </c>
       <c r="D6" t="n">
-        <v>48.51070158151941</v>
+        <v>7.882989006996905</v>
       </c>
       <c r="E6" t="n">
-        <v>25.31676038832282</v>
+        <v>4.113973563102458</v>
       </c>
       <c r="F6" t="n">
-        <v>23.84334595362643</v>
+        <v>3.874543717464294</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.19555180393673</v>
+        <v>2.469277168139719</v>
       </c>
       <c r="D7" t="n">
-        <v>14.99997835354411</v>
+        <v>2.437496482450917</v>
       </c>
       <c r="E7" t="n">
-        <v>25.31676038832282</v>
+        <v>4.113973563102458</v>
       </c>
       <c r="F7" t="n">
-        <v>23.84334595362643</v>
+        <v>3.874543717464294</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.78535021656662</v>
+        <v>6.302619410192076</v>
       </c>
       <c r="D8" t="n">
-        <v>38.29314079344719</v>
+        <v>6.222635378935169</v>
       </c>
       <c r="E8" t="n">
-        <v>25.31676038832282</v>
+        <v>4.113973563102458</v>
       </c>
       <c r="F8" t="n">
-        <v>23.84334595362643</v>
+        <v>3.874543717464294</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>52.40834733813386</v>
+        <v>8.516356442446753</v>
       </c>
       <c r="D9" t="n">
-        <v>53.54967215090293</v>
+        <v>8.701821724521727</v>
       </c>
       <c r="E9" t="n">
-        <v>25.31676038832282</v>
+        <v>4.113973563102458</v>
       </c>
       <c r="F9" t="n">
-        <v>23.84334595362643</v>
+        <v>3.874543717464294</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
